--- a/AAII_Financials/Quarterly/COP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>COP</t>
   </si>
@@ -656,540 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19400000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16008000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13675000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15376000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14319000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16909000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14676000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13482000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14023000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14269000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15150000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14638000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12763000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15310000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18558000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21013000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21161000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17762000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15120000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11326000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9556000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9826000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5491000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4386000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2749000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6111000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7635000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7752000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7908000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9131000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9120000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9784000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8935000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8699000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8547000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6737000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6777000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7497000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6958000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6513000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9143000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8559000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7602000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8489000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7657000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8694000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7384000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7008000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7022000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7349000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7711000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7538000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6502000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7917000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10620000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11050000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10975000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8332000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8023000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5528000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4363000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5810000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3609000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2802000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2177000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3807000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4027000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4032000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4061000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4926000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5292000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4915000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4401000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4858000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4786000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4131000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4218000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4452000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4315000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4352000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10257000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7449000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6073000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6887000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6662000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8215000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7292000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6474000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7001000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6920000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7439000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7100000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6261000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7393000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7938000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9963000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10186000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9430000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7097000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5798000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5193000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4016000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1882000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1584000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>572000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2304000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3608000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3720000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3847000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4205000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3828000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4869000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4534000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3841000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3761000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2606000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2559000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3045000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2643000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2161000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,19 +1244,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3">
         <v>78000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
@@ -1252,11 +1265,11 @@
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3">
         <v>81000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>24</v>
@@ -1264,11 +1277,11 @@
       <c r="L12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="3">
         <v>81000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>24</v>
@@ -1276,86 +1289,89 @@
       <c r="P12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="3">
         <v>197000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>82000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>133000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>63000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>125000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>65000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>56000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>62000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>250000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>125000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>97000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>157000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>151000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>219000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>122000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>110000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>102000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>103000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>69000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>95000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>214000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>75000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>98000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>551000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>343000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>457000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,252 +1492,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E14" s="3">
         <v>14000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-27000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-316000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-78000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>798000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>39000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-93000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-47000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-97000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>49000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-250000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-809000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>476000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-39000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-35000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>51000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>845000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-598000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>594000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>355000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-170000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-163000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-882000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-69000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-90000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>93000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-240000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>4418000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>153000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-340000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>72000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3001000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2931000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3034000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2937000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2856000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2764000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2666000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2390000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2338000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2211000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2234000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2107000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2021000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1961000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1999000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1872000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1810000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1823000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1783000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1672000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1867000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1886000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1541000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1411000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1158000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1411000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1488000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1566000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1490000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1546000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1612000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>1494000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>1438000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>1412000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>1633000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>1608000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>1625000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>1979000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>2061000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>2425000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>13287000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12478000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11446000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12371000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11494000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12398000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10819000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10209000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10236000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10484000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10722000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10509000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9391000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10809000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13676000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14028000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13889000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10049000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11412000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7841000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6772000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8297000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6892000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4576000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3147000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6127000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6596000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4573000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6199000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6728000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6581000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6973000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6441000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6937000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7172000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6021000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>11017000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7618000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6843000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>7778000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>6113000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3530000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2229000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3005000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2825000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4511000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3857000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3273000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3787000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3785000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4428000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4129000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3372000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4501000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4882000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6985000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7272000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7713000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3708000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3485000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2784000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1529000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1401000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-190000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-398000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1039000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3179000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1709000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2403000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2539000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2811000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2494000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1762000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1375000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>716000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-4240000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-121000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>115000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-1265000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,618 +2081,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-45000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>127000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-153000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-108000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-82000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-153000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-109000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-135000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>404000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-68000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-170000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>531000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>654000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>594000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>402000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>847000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>316000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>516000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>411000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>517000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-122000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>621000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1345000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>443000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>498000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>514000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>517000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>321000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>281000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>302000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>198000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>176000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>188000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>185000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>204000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>194000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>9253000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6506000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5136000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6095000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5789000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7357000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6223000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5816000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6234000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6131000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6258000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6304000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5563000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6619000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7412000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9511000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9676000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9938000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6338000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5473000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5167000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3826000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>657000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1099000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1381000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>50000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2970000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5243000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3713000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4466000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4472000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4586000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4234000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3372000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3184000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2512000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-2430000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2062000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2370000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1106000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E22" s="3">
         <v>198000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>195000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>223000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>232000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>205000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>191000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>189000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>198000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>205000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>219000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>194000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>179000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>188000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>178000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>199000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>211000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>217000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>219000</v>
       </c>
       <c r="V22" s="3">
         <v>219000</v>
       </c>
       <c r="W22" s="3">
+        <v>219000</v>
+      </c>
+      <c r="X22" s="3">
         <v>220000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>226000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>202000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>200000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>202000</v>
       </c>
       <c r="AB22" s="3">
         <v>202000</v>
       </c>
       <c r="AC22" s="3">
+        <v>202000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>196000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>184000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>165000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>233000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>188000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>186000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>184000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>226000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>251000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>306000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>315000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>317000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6082000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3363000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2245000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2928000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3017000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4466000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2970000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3235000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3659000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3808000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4264000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4100000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3362000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4562000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5235000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7440000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7655000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7898000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4336000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3582000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3080000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1714000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1086000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-512000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1563000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1286000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3493000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2058000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2687000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2672000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2906000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2619000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1776000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1325000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>653000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-4361000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-232000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-1654000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2151000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1180000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>803000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1202000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1046000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1617000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>664000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1176000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1330000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1257000</v>
       </c>
       <c r="M24" s="3">
         <v>1257000</v>
       </c>
       <c r="N24" s="3">
+        <v>1257000</v>
+      </c>
+      <c r="O24" s="3">
         <v>1302000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1130000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1986000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2913000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2510000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2139000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1709000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1203000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>989000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>732000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-314000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-62000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-257000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>148000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>543000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>422000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>461000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>841000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>804000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1033000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>965000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>876000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>579000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>217000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-935000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-831000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>11000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-628000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2183000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1442000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1726000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1971000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2849000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2306000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2059000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2329000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2551000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3007000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2798000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2232000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2920000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3249000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4527000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5145000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5759000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2627000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2379000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2091000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>982000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-772000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-450000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>278000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1711000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>743000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3071000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1597000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1846000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1868000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1873000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1654000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>900000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>746000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>436000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-3426000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>599000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-1026000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3918000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2177000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1437000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1720000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1964000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2840000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2300000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2052000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2322000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2542000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2998000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2789000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2224000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2911000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3189000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4527000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5145000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5759000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2627000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2379000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2091000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>982000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-772000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-450000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>260000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>720000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3056000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1580000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1833000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1858000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1861000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1640000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>888000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>727000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>420000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-3440000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>586000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-35000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-1040000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3221,17 +3281,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3239,11 +3299,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>10000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3251,11 +3311,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>852000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3263,14 +3323,17 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3391,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3513,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E32" s="3">
         <v>45000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-127000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>153000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>108000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>82000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>153000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>109000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>135000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-404000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>68000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>170000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>157000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-531000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-654000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-594000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-402000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-847000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-316000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-516000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-411000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-517000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>122000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-621000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1345000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-443000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-498000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-514000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-517000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-321000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-281000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-302000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-198000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-176000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-188000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-185000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-204000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-194000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2183000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1442000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1726000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1971000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2849000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2306000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2059000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2329000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2551000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3007000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2798000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2232000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2920000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3189000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4527000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5145000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5759000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2627000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2379000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2091000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>982000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-772000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-450000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>260000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>720000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3056000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1580000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1833000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1868000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1861000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1640000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>888000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1579000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>420000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-3440000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>586000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-35000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-1040000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3879,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2183000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1442000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1726000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1971000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2849000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2306000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2059000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2329000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2551000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3007000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2798000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2232000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2920000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3189000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4527000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5145000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5759000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2627000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2379000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2091000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>982000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-772000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-450000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>260000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>720000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3056000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1580000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1833000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1868000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1861000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1640000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>888000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1579000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>420000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-3440000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>586000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-35000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-1040000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4172,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4216,984 +4301,1009 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6574000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5877000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6497000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5260000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4901000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6309000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5607000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5221000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4294000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5574000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5635000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8830000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5735000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6974000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6458000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8010000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6909000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6414000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5028000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9833000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6608000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2831000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2991000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2490000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2907000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3908000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5088000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7193000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5941000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6218000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5915000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3716000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3234000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4984000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6325000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6911000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>7534000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3109000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3610000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4090000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="E42" s="3">
         <v>486000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>484000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>996000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>439000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>926000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>507000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1571000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1723000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>487000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>971000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>616000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1080000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1635000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2785000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2412000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1272000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>730000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>446000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>678000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2251000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4104000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3609000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4032000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3985000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3866000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3028000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>908000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>732000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>249000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>248000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>875000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>612000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>288000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1873000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2696000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2733000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>252000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>50000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6957000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7050000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5813000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5744000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5701000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6400000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6695000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4815000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5307000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5458000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5474000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5671000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4531000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5296000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7088000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7354000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8153000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7879000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6670000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5465000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4524000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4481000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2754000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2119000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1532000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2264000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3401000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3616000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3651000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3869000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4067000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4499000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3930000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4192000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4320000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3364000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3163000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3359000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3414000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3320000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1879000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1910000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1873000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1721000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1897000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1844000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1809000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1496000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1447000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1443000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1398000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1326000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1236000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1258000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1219000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1226000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1234000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1174000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1208000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1043000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1138000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1098000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1002000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>982000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>726000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>955000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1089000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1014000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1007000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1239000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1093000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1053000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1060000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1023000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1019000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1097000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1018000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1108000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>2595000</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>491000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1639000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>454000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1037000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>394000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>342000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>512000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>611000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>582000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>793000</v>
       </c>
-      <c r="P45" s="3" t="s">
+      <c r="Q45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1199000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1451000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1292000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1389000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2698000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3162000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2651000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2100000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1710000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1384000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1647000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2380000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4370000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2545000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4387000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2333000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2037000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4394000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2739000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2670000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2934000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2960000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>5430000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2911000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>517000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>889000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19195000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16229000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15532000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15884000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13939000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16906000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15647000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13984000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13734000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13721000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14330000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17181000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13501000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16116000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18749000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20453000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18860000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17586000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16050000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20181000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17172000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14614000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12066000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11059000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11053000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13144000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16913000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15217000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15800000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13683000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13274000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14723000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>11608000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13187000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>16512000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>16954000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>19879000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>10728000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>8609000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>9641000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10345000</v>
+      </c>
+      <c r="E47" s="3">
         <v>10320000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10075000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10074000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10361000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10008000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9756000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9192000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9304000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9132000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8987000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8731000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8618000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8197000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8225000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8204000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8203000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8309000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7113000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8058000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8072000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8345000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8131000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8409000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8501000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8874000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8906000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9135000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9016000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>9570000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>9664000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>9888000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>9834000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>9971000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>10060000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>10157000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>10203000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>21675000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>21672000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>21864000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>91248000</v>
+      </c>
+      <c r="E48" s="3">
         <v>93141000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>94189000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>93498000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>95242000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>94316000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>95373000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>70725000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70226000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>69907000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70735000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65561000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>65452000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>65090000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>65402000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>63673000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>64008000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>64642000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64911000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>56689000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>57717000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>58270000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40676000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41269000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41120000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>40645000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>43165000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>44619000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>45381000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>45942000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>45698000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>44736000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>46306000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>45997000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>45683000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>46669000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>46846000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>54440000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>58331000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>61649000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5314,8 +5424,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5436,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5558,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3473000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3035000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2143000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3016000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3057000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3024000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2004000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2798000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2730000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2588000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1872000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2178000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2034000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2038000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1453000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2507000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2622000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2771000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2587000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2376000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2442000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2464000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1745000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2420000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2372000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2370000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1530000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1369000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2303000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1344000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1209000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1572000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1107000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1081000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1076000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1130000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1160000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1130000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5802,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>124261000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122725000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>121939000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122472000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122599000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>124254000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>122780000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>96699000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>95994000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>95348000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>95924000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>93651000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>89605000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>91441000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>93829000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>94837000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>93693000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>93308000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>90661000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>87304000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>85403000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>83693000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62618000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>63157000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>63046000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>65033000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70514000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70340000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>71261000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>71498000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>69980000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>70556000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>68936000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>70727000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>73362000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>74861000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>78004000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>87973000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>89772000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>94284000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5968,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6012,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6764000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7017000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6218000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6245000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6517000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7349000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6044000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5161000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5065000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5101000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5083000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5143000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4626000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5078000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6163000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6268000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5873000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4897000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5025000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4131000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3613000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3801000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2698000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2239000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2080000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2921000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3200000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3171000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3635000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3846000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3895000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3918000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3666000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3886000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4030000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3416000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3434000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3531000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3653000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3751000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1065000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1403000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1016000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>414000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>608000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1364000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1314000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1312000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1113000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1267000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>881000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>879000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1317000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>417000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>664000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>676000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1160000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1200000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>920000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1205000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>689000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>619000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>482000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>146000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>126000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>105000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>121000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>114000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>113000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>112000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>95000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>337000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2575000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1331000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3798000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1095000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1089000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1336000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3585000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3232000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2643000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2330000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2196000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3574000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3189000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2781000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2499000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2685000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2569000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2425000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2441000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3816000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6267000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7065000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5667000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5567000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5796000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5398000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3332000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2694000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2049000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1919000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1879000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3028000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3738000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2650000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5247000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3411000</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>3388000</v>
       </c>
       <c r="AH59" s="3">
         <v>3388000</v>
       </c>
       <c r="AI59" s="3">
+        <v>3388000</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>2883000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2886000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2792000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2384000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2694000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2900000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2167000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2450000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12452000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12586000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11972000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12009000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10986000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13329000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12124000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10765000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10324000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10163000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10005000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10338000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9548000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11553000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12847000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13997000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12216000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11624000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12021000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10449000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8150000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7184000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5366000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4640000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4105000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6075000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7043000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5942000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8996000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7370000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7395000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7401000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6638000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7109000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9397000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7131000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>9926000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7526000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>6909000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>7537000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>22828000</v>
+      </c>
+      <c r="E61" s="3">
         <v>22262000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22991000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22466000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23115000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23176000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23984000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16990000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17040000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17304000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18367000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18182000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15565000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15266000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16226000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16297000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16295000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17586000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18734000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18748000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18805000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19338000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14750000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14905000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14852000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14847000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14790000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14799000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14809000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14832000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14856000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14902000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14885000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>16709000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>17128000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>19673000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>19670000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>25340000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>26186000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>27353000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10312000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10003000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9283000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10015000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10161000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10029000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9428000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9132000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8968000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8813000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8451000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8105000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7942000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7905000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16753000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15464000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14980000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14880000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>14500000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13992000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>14172000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>14016000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12653000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12829000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12596000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12724000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13631000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>14360000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14382000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16315000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>15665000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16174000</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>16191000</v>
       </c>
       <c r="AJ62" s="3">
         <v>16191000</v>
       </c>
       <c r="AK62" s="3">
+        <v>16191000</v>
+      </c>
+      <c r="AL62" s="3">
         <v>16036000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17345000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>17909000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>19506000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>21451000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>22938000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6866,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7110,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58912000</v>
+      </c>
+      <c r="E66" s="3">
         <v>58184000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57452000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57549000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57027000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>59016000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57984000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>46818000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46249000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46023000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46645000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45906000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42074000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43658000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45826000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45758000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>43491000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>44090000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45255000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43189000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>41127000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>40538000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32769000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32374000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>31553000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33718000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>35533000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35194000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38285000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>38639000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>38041000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38606000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37894000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>40181000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>42755000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>44361000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>47718000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>52620000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>54798000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>58114000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7276,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7398,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7520,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7642,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7764,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72921000</v>
+      </c>
+      <c r="E72" s="3">
         <v>70016000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>68864000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>68459000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>67707000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66721000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>64869000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>63459000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>62309000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>60895000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>59268000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56952000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55483000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>54593000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>53029000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>51278000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>49093000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>45442000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>40674000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38307000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37116000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35608000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35213000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36448000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>37351000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>37545000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>39742000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>39484000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36769000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35534000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>34010000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>32495000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30967000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>29663000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>29391000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>28130000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>28033000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>31804000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>31548000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>31896000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8008,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8130,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8252,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>65349000</v>
+      </c>
+      <c r="E76" s="3">
         <v>64541000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64487000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64923000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>65572000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>65238000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>64796000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49881000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49745000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49325000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49279000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47745000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47531000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47783000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48003000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49079000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>50202000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49218000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45406000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>44115000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>44276000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>43155000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29849000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>30783000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>31493000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>31315000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>34981000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35146000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32976000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32859000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>31939000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>31950000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>31042000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>30546000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>30607000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>30500000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>30286000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>35353000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>34974000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>36170000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8496,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2183000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1442000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1726000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1971000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2849000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2306000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2059000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2329000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2551000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3007000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2798000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2232000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2920000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3189000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4527000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5145000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5759000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2627000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2379000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2091000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>982000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-772000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-450000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>260000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>720000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3056000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1580000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1833000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1868000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1861000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1640000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>888000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1579000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>420000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-3440000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>586000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-35000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-1040000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8789,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2838000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2746000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2664000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2390000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2334000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2211000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2223000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2095000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2010000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1942000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1999000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1872000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1810000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1823000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1999000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1872000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1810000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1823000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1783000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1672000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1867000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1886000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1541000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1411000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1158000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1411000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1488000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1566000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1490000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1546000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1612000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1494000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1438000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1412000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1633000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1608000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1625000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1979000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2061000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>2425000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9033,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9155,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9277,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9399,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9521,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7434000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4295000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4318000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5878000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3485000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6115000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4457000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5763000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4919000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4985000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5263000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5445000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3854000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5403000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6592000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8740000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7914000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5068000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5868000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4797000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4251000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2080000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1672000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>868000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>157000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2982000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2337000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2891000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2894000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3783000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3410000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3342000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2399000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2481000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1055000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1751000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1790000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1443000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1280000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9687,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3024000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2948000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3023000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2866000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3286000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3378000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3317000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2916000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2969000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2916000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2883000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2545000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2923000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2897000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2533000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2497000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1968000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3161000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1302000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2448000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1058000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-876000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1649000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1595000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1675000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1729000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1617000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1599000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1999000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1535000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1517000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1088000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1020000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-966000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-999000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-916000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9931,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10053,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3511000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2808000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-850000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3179000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2461000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2346000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2200000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2658000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4151000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2141000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5852000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2384000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2316000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1448000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2934000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3105000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2091000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-611000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8595000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>532000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>734000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1215000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-543000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1116000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-530000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1932000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3830000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>150000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1461000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-178000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1638000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1949000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-78000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-469000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>2008000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>7197000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-974000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>53000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>275000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10219,130 +10451,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1032000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1038000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>975000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>984000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>998000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>897000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>910000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>915000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>924000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1408000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1337000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1350000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1488000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2390000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1484000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-988000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-864000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-609000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-579000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-583000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-588000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-464000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-454000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-455000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-458000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-463000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-341000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-346000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-350000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-354000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-334000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-337000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-338000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-319000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-324000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-331000</v>
       </c>
       <c r="AN96" s="3">
         <v>-331000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-331000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-313000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-314000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10463,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10585,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10707,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3170000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2186000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2158000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2324000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2483000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3137000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1769000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2198000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2043000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2825000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2639000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>29000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2725000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3326000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5508000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4330000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5078000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3137000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2031000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2086000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1203000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1015000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-652000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-177000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-649000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1230000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1654000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1173000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1317000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1263000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3003000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3776000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2586000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3827000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-4599000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1344000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1906000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-347000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E101" s="3">
         <v>83000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-105000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>41000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-73000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>51000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-58000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-104000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>228000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-215000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-258000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>21000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>228000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-215000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-258000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>21000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-31000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>11000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>42000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>31000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>29000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-122000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>22000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>75000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-77000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-139000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>125000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>141000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>76000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>27000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>719000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-670000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1317000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>373000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1394000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>715000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>383000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>948000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1271000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3177000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3102000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1245000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>525000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1622000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1090000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>487000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1341000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4789000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3231000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3793000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-152000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>519000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-394000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-993000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1179000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2096000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1261000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-273000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>319000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2211000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>483000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1749000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1330000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-586000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-623000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>4425000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-501000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-480000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1227000</v>
       </c>
     </row>
